--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7FABCEE-DE6E-44D7-91C5-459474C189AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1464DD0-E1F7-4A04-96DC-277F97314058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6848,7 +6848,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32EA7D6E-ED3B-4A7C-A2ED-36F80BE0D67A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A358ECA-1BB9-4B58-9D6C-A0966DD58303}">
   <dimension ref="B2:C948"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1464DD0-E1F7-4A04-96DC-277F97314058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{911546D3-477E-4196-8098-A908735F874F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6848,7 +6848,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A358ECA-1BB9-4B58-9D6C-A0966DD58303}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A758940-2545-47F1-B237-73728EA8F4C7}">
   <dimension ref="B2:C948"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{911546D3-477E-4196-8098-A908735F874F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C35A7495-52D0-4EA5-8509-BBC82D2FB272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6848,7 +6848,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A758940-2545-47F1-B237-73728EA8F4C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E79C558A-5A8F-4B52-A255-6FE171F86FD4}">
   <dimension ref="B2:C948"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56F29B4A-42B0-4819-8A6B-A26A99E057DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F6BA8A8-ED21-4604-9742-1E4901FDF1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91CF07B2-71B4-480B-87A1-962A3C309376}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{218CDED9-E608-439D-AB92-39878FF0DFC1}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F6BA8A8-ED21-4604-9742-1E4901FDF1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{12A709ED-74B2-4BDF-9A78-06760544A18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{218CDED9-E608-439D-AB92-39878FF0DFC1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F22C659-F492-4963-A7D9-FF61018CE711}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12A709ED-74B2-4BDF-9A78-06760544A18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D32E7358-77F8-45ED-AAC6-FEA3D2F56B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F22C659-F492-4963-A7D9-FF61018CE711}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A99837-4018-4393-B87A-3DBA9751DE5B}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D32E7358-77F8-45ED-AAC6-FEA3D2F56B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{19E15A1C-F7C2-4EE6-A5C3-C437DE08D163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A99837-4018-4393-B87A-3DBA9751DE5B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCB75A05-A29A-4F89-BD74-D934B7C9E846}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19E15A1C-F7C2-4EE6-A5C3-C437DE08D163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A9CE425-E269-47C7-A02D-E3FAE5BCDE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCB75A05-A29A-4F89-BD74-D934B7C9E846}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8970E59-E72D-4073-A5B2-06A271B4AA40}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A9CE425-E269-47C7-A02D-E3FAE5BCDE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52F4340D-BDB9-470E-9AC8-03BF850FBEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8970E59-E72D-4073-A5B2-06A271B4AA40}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0214C0-83DC-4118-BF69-441BA3D5289A}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52F4340D-BDB9-470E-9AC8-03BF850FBEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{87BB17CD-8EB4-4131-948C-5F64984461A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0214C0-83DC-4118-BF69-441BA3D5289A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26ACFAB1-0FE9-48D1-9F1D-A88D8CFC1624}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87BB17CD-8EB4-4131-948C-5F64984461A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03C18309-072A-4B66-AD34-4EA0CE93140D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26ACFAB1-0FE9-48D1-9F1D-A88D8CFC1624}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B7CBCD9-1EB6-4E10-BA94-321FE2A87827}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03C18309-072A-4B66-AD34-4EA0CE93140D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB555E4B-8C80-4CC1-BBD2-4D1C217520BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B7CBCD9-1EB6-4E10-BA94-321FE2A87827}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BEA4E47-9212-43F7-90B8-A6AC6A23DCF6}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB555E4B-8C80-4CC1-BBD2-4D1C217520BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{25ACB3AC-EEC5-48F7-A137-90CD32A46316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BEA4E47-9212-43F7-90B8-A6AC6A23DCF6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DACF78A1-969D-4F64-B95D-033BC93C64CC}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25ACB3AC-EEC5-48F7-A137-90CD32A46316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FACA893A-FAB5-4464-AAF7-0337EDFAF24C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DACF78A1-969D-4F64-B95D-033BC93C64CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{063AD3D8-2901-4C75-85F9-217261FFCF5D}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FACA893A-FAB5-4464-AAF7-0337EDFAF24C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAA9422D-DF63-499A-B54D-2016F80B79E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{063AD3D8-2901-4C75-85F9-217261FFCF5D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5969EB66-950D-4C5E-B663-36585D19B9CD}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAA9422D-DF63-499A-B54D-2016F80B79E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{31E8B30D-9E1E-49A9-9240-B3D3174C2611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5969EB66-950D-4C5E-B663-36585D19B9CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71FD0E6C-61D2-442F-AD76-5DA4E8354EC6}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31E8B30D-9E1E-49A9-9240-B3D3174C2611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{64FC5358-2C75-4B30-B1BF-F72EEBF81D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71FD0E6C-61D2-442F-AD76-5DA4E8354EC6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2EE4C92-7FCF-4D8F-8F70-F9333E21F5E6}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64FC5358-2C75-4B30-B1BF-F72EEBF81D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{400BA610-5FE6-449F-BE93-7B77C7404225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2EE4C92-7FCF-4D8F-8F70-F9333E21F5E6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30F8018C-A3DF-4C19-9B00-78FF90DFE261}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{400BA610-5FE6-449F-BE93-7B77C7404225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6053F924-9C00-4940-8080-4C9309A8DC8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30F8018C-A3DF-4C19-9B00-78FF90DFE261}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF5313E0-20AA-408F-B0CF-B2E5A7E413D6}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6053F924-9C00-4940-8080-4C9309A8DC8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03783062-B0BF-4B88-9F80-A46D1D4EEC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF5313E0-20AA-408F-B0CF-B2E5A7E413D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{958EBB96-6B68-4AAF-ADE0-5A1C8FD3AAD6}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03783062-B0BF-4B88-9F80-A46D1D4EEC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{86C73AD1-8620-4486-A7D5-CCBEE4F7CFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{958EBB96-6B68-4AAF-ADE0-5A1C8FD3AAD6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0156B21B-59DA-477F-A3D2-D35D2122C4D8}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{86C73AD1-8620-4486-A7D5-CCBEE4F7CFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5558479E-1678-443B-B31F-599114DE6BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="12683" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0156B21B-59DA-477F-A3D2-D35D2122C4D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6014A9F0-B8E0-4A11-8869-CE16324D4725}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5558479E-1678-443B-B31F-599114DE6BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFD14D31-DF61-44FE-8DDF-9786D79EE039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="12683" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6014A9F0-B8E0-4A11-8869-CE16324D4725}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E4AFC0A-B632-4FF3-9101-05030BF63FF9}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFD14D31-DF61-44FE-8DDF-9786D79EE039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2A9566B-ED11-4FC5-A3DC-3D94803EB506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4043" yWindow="4043" windowWidth="21599" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E4AFC0A-B632-4FF3-9101-05030BF63FF9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF63ED8A-CD0A-4A6F-9BD6-A3B5E2D1950D}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2A9566B-ED11-4FC5-A3DC-3D94803EB506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE2E080E-6A4A-4C77-A304-8DAC1A0B1FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4043" yWindow="4043" windowWidth="21599" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -5255,7 +5255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF63ED8A-CD0A-4A6F-9BD6-A3B5E2D1950D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6E98EF-864C-434F-BD1A-AF3B933416B7}">
   <dimension ref="B9:E688"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E987DA1A-F87C-4AF9-9113-992D2D7B929D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44499E41-CA7D-49EF-BF54-060E3AB6236F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72CBFEF4-9A90-43FC-80A2-1835D6CC704E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E520A6-008A-418F-A905-A4E5414323E5}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44499E41-CA7D-49EF-BF54-060E3AB6236F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46C51967-E77D-4200-86FF-2C80E3CECBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E520A6-008A-418F-A905-A4E5414323E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF1AE1A6-7406-43BB-BB0B-095779E7D117}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46C51967-E77D-4200-86FF-2C80E3CECBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3ABAF54-2FE4-47BB-8286-32640961A3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF1AE1A6-7406-43BB-BB0B-095779E7D117}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BB518EA-5764-437C-A5F1-374185AE1985}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3ABAF54-2FE4-47BB-8286-32640961A3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A783471-9FAE-4A70-BB09-B647F5099471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BB518EA-5764-437C-A5F1-374185AE1985}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AEFE49B-4B63-4D4F-B9FD-B7D99DD9022D}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A783471-9FAE-4A70-BB09-B647F5099471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A1C3A42-D0AA-4C04-AA11-4D58FB33B574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AEFE49B-4B63-4D4F-B9FD-B7D99DD9022D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67988760-A5B9-4812-9443-6F1095305137}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A1C3A42-D0AA-4C04-AA11-4D58FB33B574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{81801BEE-4D73-4427-ADCA-D0621A186AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67988760-A5B9-4812-9443-6F1095305137}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73C369D5-26D1-41C2-A575-701402DB15EE}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{81801BEE-4D73-4427-ADCA-D0621A186AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D508438F-5677-472D-A2B0-18B779832A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73C369D5-26D1-41C2-A575-701402DB15EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFDBC9BD-8423-4ABE-8729-DE4FE8F3C8CF}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D508438F-5677-472D-A2B0-18B779832A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE60A85B-3079-4ADD-B693-DEEEEA74E125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFDBC9BD-8423-4ABE-8729-DE4FE8F3C8CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64ECF854-8977-4AAF-82AC-172450F243F3}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE60A85B-3079-4ADD-B693-DEEEEA74E125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{70411E95-C29A-4903-A73D-8553093CA5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64ECF854-8977-4AAF-82AC-172450F243F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{183EC794-7D4A-4320-8568-1CA6E8BDEFDA}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70411E95-C29A-4903-A73D-8553093CA5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{20AB8DE8-0D3A-484C-AFB5-99021D2C9D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{183EC794-7D4A-4320-8568-1CA6E8BDEFDA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21CE6CE7-D35A-40C5-88DC-89526F7E7078}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{20AB8DE8-0D3A-484C-AFB5-99021D2C9D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9173DC89-D03D-493C-8499-983173C8F695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21CE6CE7-D35A-40C5-88DC-89526F7E7078}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC2033A-E073-4B4C-A88C-0C0625C6C29C}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9173DC89-D03D-493C-8499-983173C8F695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5EF14762-6BAC-4601-93D9-A85EFA1E49F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC2033A-E073-4B4C-A88C-0C0625C6C29C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4D7191B-09A8-4569-A4F2-E7F2952B109E}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5EF14762-6BAC-4601-93D9-A85EFA1E49F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5728AC51-A5B6-4A69-B811-2D4350A9E69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4D7191B-09A8-4569-A4F2-E7F2952B109E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBAC453B-F1FB-4D08-A5E8-07AF73C13AC3}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5728AC51-A5B6-4A69-B811-2D4350A9E69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC4AA672-8EAF-4680-BF6F-543529DE1F8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBAC453B-F1FB-4D08-A5E8-07AF73C13AC3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5312BD86-BF60-4A78-8B6C-ED182961FEDC}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC4AA672-8EAF-4680-BF6F-543529DE1F8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0D86FC6-FC81-4024-A75A-C046C083A40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5312BD86-BF60-4A78-8B6C-ED182961FEDC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5F609E2-EA15-43EF-804C-897D4C84FC0D}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0D86FC6-FC81-4024-A75A-C046C083A40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{45C8983F-4AFA-470A-82AE-41A7F6059208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5F609E2-EA15-43EF-804C-897D4C84FC0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BBEDBED-A0DF-48D4-B176-038AF5D19DD5}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45C8983F-4AFA-470A-82AE-41A7F6059208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{688C877F-075D-42B5-821D-CFE323522C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BBEDBED-A0DF-48D4-B176-038AF5D19DD5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBF2C63E-AD82-4C61-9FBE-9F2E7A072D9C}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{688C877F-075D-42B5-821D-CFE323522C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4EFDC2B-C319-422E-89E3-DEEDFB80AC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBF2C63E-AD82-4C61-9FBE-9F2E7A072D9C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45CEE3A8-162C-408F-A8CB-03BABEDD15DC}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4EFDC2B-C319-422E-89E3-DEEDFB80AC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AC4FA2D-CC29-4131-8F41-AC792121EAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45CEE3A8-162C-408F-A8CB-03BABEDD15DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0801C50-81AF-4D7E-823F-EA7FDE64A0D6}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AC4FA2D-CC29-4131-8F41-AC792121EAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC6FBD36-744F-4329-BE2E-8378938A5038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0801C50-81AF-4D7E-823F-EA7FDE64A0D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FED2588-0093-47C5-901D-83802EFFC5E7}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC6FBD36-744F-4329-BE2E-8378938A5038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73DCB839-22E9-470B-BDDB-033FEAD9D804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FED2588-0093-47C5-901D-83802EFFC5E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3945F54-0459-430F-ADD7-3B31EA8F4265}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73DCB839-22E9-470B-BDDB-033FEAD9D804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DB3ED15-F0EB-4894-8952-6F480BA4ADAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3945F54-0459-430F-ADD7-3B31EA8F4265}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5412661A-AB81-4E5B-9472-022B6107C4EE}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DB3ED15-F0EB-4894-8952-6F480BA4ADAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7C5E314-4720-427E-BA88-507EB0D122BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5412661A-AB81-4E5B-9472-022B6107C4EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11EA87FC-E0E3-474F-8466-066863D2F3C3}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7C5E314-4720-427E-BA88-507EB0D122BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E1C8664-86AD-4C0B-8520-DF68788BC34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11EA87FC-E0E3-474F-8466-066863D2F3C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABDC66FE-D2EC-46B8-B7AD-F5ADD411C1D1}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E1C8664-86AD-4C0B-8520-DF68788BC34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8621FD8-08A2-4983-A858-A095778B096C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABDC66FE-D2EC-46B8-B7AD-F5ADD411C1D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9A0BAAF-8981-4053-B82A-205920A3D9A5}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_ITA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8621FD8-08A2-4983-A858-A095778B096C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{57B98231-12E4-44C6-8B65-05D7E6D1EEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3113,7 +3113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9A0BAAF-8981-4053-B82A-205920A3D9A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B7DC822-F92A-429A-9038-BBD0026B52D2}">
   <dimension ref="B9:E331"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
